--- a/artfynd/A 48061-2022 artfynd.xlsx
+++ b/artfynd/A 48061-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120726462</v>
+        <v>120726465</v>
       </c>
       <c r="B2" t="n">
-        <v>91365</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560865</v>
+        <v>560864</v>
       </c>
       <c r="R2" t="n">
-        <v>7054678</v>
+        <v>7054706</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120726461</v>
+        <v>120726458</v>
       </c>
       <c r="B3" t="n">
-        <v>91365</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560867</v>
+        <v>560905</v>
       </c>
       <c r="R3" t="n">
-        <v>7054654</v>
+        <v>7054587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120726465</v>
+        <v>120726463</v>
       </c>
       <c r="B4" t="n">
-        <v>90968</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560864</v>
+        <v>560866</v>
       </c>
       <c r="R4" t="n">
-        <v>7054706</v>
+        <v>7054705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120726463</v>
+        <v>120726459</v>
       </c>
       <c r="B5" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560866</v>
+        <v>560930</v>
       </c>
       <c r="R5" t="n">
-        <v>7054705</v>
+        <v>7054587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1119,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120726459</v>
+        <v>120726461</v>
       </c>
       <c r="B6" t="n">
-        <v>91122</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560930</v>
+        <v>560867</v>
       </c>
       <c r="R6" t="n">
-        <v>7054587</v>
+        <v>7054654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120726458</v>
+        <v>120726462</v>
       </c>
       <c r="B7" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560905</v>
+        <v>560865</v>
       </c>
       <c r="R7" t="n">
-        <v>7054587</v>
+        <v>7054678</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 48061-2022 artfynd.xlsx
+++ b/artfynd/A 48061-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726465</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726458</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726463</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726459</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726461</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,8 +1368,21 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726462</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>